--- a/Paper2_Package/03_RESULTS/Task7_action_direction/task7_supporting.xlsx
+++ b/Paper2_Package/03_RESULTS/Task7_action_direction/task7_supporting.xlsx
@@ -732,7 +732,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E5"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -743,20 +743,15 @@
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>ambiguous</t>
+          <t>reversal-consistent</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>reversal-consistent</t>
+          <t>reversal-inconsistent</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
-        <is>
-          <t>reversal-inconsistent</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
@@ -769,15 +764,12 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0</v>
+        <v>66</v>
       </c>
       <c r="C2" t="n">
-        <v>66</v>
+        <v>8</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
-      </c>
-      <c r="E2" t="n">
         <v>289</v>
       </c>
     </row>
@@ -788,16 +780,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>3</v>
+        <v>18</v>
       </c>
       <c r="C3" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="D3" t="n">
-        <v>24</v>
-      </c>
-      <c r="E3" t="n">
-        <v>453</v>
+        <v>456</v>
       </c>
     </row>
     <row r="4">
@@ -807,16 +796,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>1</v>
+        <v>39</v>
       </c>
       <c r="C4" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="D4" t="n">
-        <v>78</v>
-      </c>
-      <c r="E4" t="n">
-        <v>476</v>
+        <v>477</v>
       </c>
     </row>
     <row r="5">
@@ -826,16 +812,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4</v>
+        <v>294</v>
       </c>
       <c r="C5" t="n">
-        <v>294</v>
+        <v>277</v>
       </c>
       <c r="D5" t="n">
-        <v>277</v>
-      </c>
-      <c r="E5" t="n">
-        <v>1710</v>
+        <v>1714</v>
       </c>
     </row>
   </sheetData>
